--- a/evaluation_multimodels/runs/2026-09-21-minimal32-five-self-included/pairs/qwen_qwen3.8-max_judge_medium__vs__kimi_kimi-k2.6_judge_high.xlsx
+++ b/evaluation_multimodels/runs/2026-09-21-minimal32-five-self-included/pairs/qwen_qwen3.8-max_judge_medium__vs__kimi_kimi-k2.6_judge_high.xlsx
@@ -2051,33 +2051,35 @@
       <c r="H2" t="b">
         <v>1</v>
       </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>16754.60529100383</v>
+        <v>13175.1515410142</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0338749960064888</v>
+        <v>1694.192541006487</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2116,33 +2118,35 @@
       <c r="H3" t="b">
         <v>1</v>
       </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>12640.87549998658</v>
+        <v>15937.30054202024</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0107910018414259</v>
+        <v>1521.965624997392</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2181,33 +2185,35 @@
       <c r="H4" t="b">
         <v>1</v>
       </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>0.009540992323309183</v>
+        <v>10493.21445799433</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01754099503159523</v>
+        <v>1446.088500029873</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2246,33 +2252,35 @@
       <c r="H5" t="b">
         <v>1</v>
       </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>12912.51599998213</v>
+        <v>10618.48970799474</v>
       </c>
       <c r="M5" t="n">
-        <v>0.008583010639995337</v>
+        <v>2295.636333001312</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2311,33 +2319,35 @@
       <c r="H6" t="b">
         <v>1</v>
       </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>92327.51595799346</v>
+        <v>15418.82354096742</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0113330315798521</v>
+        <v>1093.096541997511</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2376,33 +2386,35 @@
       <c r="H7" t="b">
         <v>1</v>
       </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>3686.84816599125</v>
+        <v>14560.7563329977</v>
       </c>
       <c r="M7" t="n">
-        <v>0.04004203947260976</v>
+        <v>2172.690999985207</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2441,33 +2453,35 @@
       <c r="H8" t="b">
         <v>1</v>
       </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>0.00362499849870801</v>
+        <v>13781.76024998538</v>
       </c>
       <c r="M8" t="n">
-        <v>0.010124989785254</v>
+        <v>1672.803582972847</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2506,33 +2520,35 @@
       <c r="H9" t="b">
         <v>1</v>
       </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>0.00508397351950407</v>
+        <v>11383.92991700675</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01191697083413601</v>
+        <v>1823.934208019637</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2571,33 +2587,35 @@
       <c r="H10" t="b">
         <v>1</v>
       </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>86434.60304202745</v>
+        <v>13491.58487503882</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01441698987036943</v>
+        <v>2005.807708017528</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2636,33 +2654,35 @@
       <c r="H11" t="b">
         <v>1</v>
       </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>19020.59445896884</v>
+        <v>11877.63450003695</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0332500203512609</v>
+        <v>1789.173582976218</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2701,33 +2721,35 @@
       <c r="H12" t="b">
         <v>1</v>
       </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>6978.484874998685</v>
+        <v>13555.31366699142</v>
       </c>
       <c r="M12" t="n">
-        <v>0.01054099993780255</v>
+        <v>1288.009124982636</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2766,33 +2788,35 @@
       <c r="H13" t="b">
         <v>1</v>
       </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>0.01966697163879871</v>
+        <v>11337.77829201426</v>
       </c>
       <c r="M13" t="n">
-        <v>0.008500006515532732</v>
+        <v>1360.672875016462</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2831,33 +2855,35 @@
       <c r="H14" t="b">
         <v>1</v>
       </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>84048.57741697924</v>
+        <v>13134.52550000511</v>
       </c>
       <c r="M14" t="n">
-        <v>0.01429097028449178</v>
+        <v>2107.661124959122</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2896,33 +2922,35 @@
       <c r="H15" t="b">
         <v>1</v>
       </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>10092.44812501129</v>
+        <v>13222.03941602493</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0338749960064888</v>
+        <v>1458.288875001017</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2961,33 +2989,35 @@
       <c r="H16" t="b">
         <v>1</v>
       </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>6344.577124982607</v>
+        <v>11720.62762500718</v>
       </c>
       <c r="M16" t="n">
-        <v>0.01779204467311502</v>
+        <v>1103.878875030205</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -3026,33 +3056,35 @@
       <c r="H17" t="b">
         <v>1</v>
       </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>0.007291033398360014</v>
+        <v>14035.2761670365</v>
       </c>
       <c r="M17" t="n">
-        <v>0.01779105514287949</v>
+        <v>3166.28020798089</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -3091,33 +3123,35 @@
       <c r="H18" t="b">
         <v>1</v>
       </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>0.007874972652643919</v>
+        <v>10263.88929103268</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0225419644266367</v>
+        <v>1090.375417028554</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
